--- a/output/pdf_financials_xlsx/AMY.xlsx
+++ b/output/pdf_financials_xlsx/AMY.xlsx
@@ -1319,31 +1319,31 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.600568</v>
+        <v>-2.600568</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.616703</v>
+        <v>-5.616703</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.879361</v>
+        <v>-2.879361</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.47328</v>
+        <v>-0.47328</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>6.118362</v>
+        <v>-6.118362</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.81027</v>
+        <v>-0.81027</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.006934</v>
+        <v>-2.006934</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.426494</v>
+        <v>-2.426494</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>8.054671000000001</v>
+        <v>-8.054671000000001</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0.375126</v>
@@ -1627,31 +1627,31 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.600568</v>
+        <v>-2.600568</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.616703</v>
+        <v>-5.616703</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.879361</v>
+        <v>-2.879361</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.47328</v>
+        <v>-0.47328</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6.118362</v>
+        <v>-6.118362</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.81027</v>
+        <v>-0.81027</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.006934</v>
+        <v>-2.006934</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.426494</v>
+        <v>-2.426494</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>8.054671000000001</v>
+        <v>-8.054671000000001</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0.375126</v>
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.600568</v>
+        <v>-2.600568</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.616703</v>
+        <v>-5.616703</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.879361</v>
+        <v>-2.879361</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.47328</v>
+        <v>-0.47328</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.118362</v>
+        <v>-6.118362</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.81027</v>
+        <v>-0.81027</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.006934</v>
+        <v>-2.006934</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.426494</v>
+        <v>-2.426494</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>8.054671000000001</v>
+        <v>-8.054671000000001</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0.375126</v>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-86.68559999999999</v>
+        <v>86.68559999999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-112.33406</v>
+        <v>112.33406</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-95.9787</v>
+        <v>95.9787</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-122.36724</v>
+        <v>122.36724</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-121.3247</v>
+        <v>121.3247</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-161.09342</v>
+        <v>161.09342</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2071,31 +2071,31 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.623839</v>
+        <v>-2.577297</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.658249</v>
+        <v>-5.575157</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.881513</v>
+        <v>-2.877209</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.473644</v>
+        <v>-0.472916</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.118484</v>
+        <v>-6.11824</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.810302</v>
+        <v>-0.810238</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.00702</v>
+        <v>-2.006848</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.426629</v>
+        <v>-2.426359</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>8.055066999999999</v>
+        <v>-8.054275000000001</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0.374769</v>
@@ -2195,31 +2195,31 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.623839</v>
+        <v>-2.577297</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.658249</v>
+        <v>-5.575157</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.881513</v>
+        <v>-2.877209</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.473644</v>
+        <v>-0.472916</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.118484</v>
+        <v>-6.11824</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.810302</v>
+        <v>-0.810238</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.00702</v>
+        <v>-2.006848</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.426629</v>
+        <v>-2.426359</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.055066999999999</v>
+        <v>-8.054275000000001</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.374769</v>
@@ -2349,31 +2349,31 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>0</v>
@@ -6095,52 +6095,52 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.881936</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.642527</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.163546</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.528723</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.532313</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.532313</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.810053</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.228838</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.777217</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.148201</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>12.472112</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>21.575753</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>34.930932</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>36.902524</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>40.139956</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>39.034106</v>
       </c>
     </row>
     <row r="93">
@@ -7645,43 +7645,43 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-2.350223</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-3.05005</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.206788</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.028228</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002152</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.006217</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.02403</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.020329</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.042228</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.046175</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.057808</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.116452</v>
+        <v>-0.122527</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.66628</v>
+        <v>0.647191</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
@@ -9997,7 +9997,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10086,7 +10090,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11265,7 +11273,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11356,7 +11368,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -13110,7 +13126,11 @@
           <t>Share‐based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13209,7 +13229,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14947,7 +14971,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15032,7 +15060,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16208,7 +16240,11 @@
           <t>Share‐based payments reserve</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -22127,7 +22163,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -24297,7 +24337,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -27790,7 +27834,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -29103,7 +29151,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -30216,7 +30268,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -36940,10 +36996,10 @@
         </is>
       </c>
       <c r="N286" s="5" t="n">
-        <v>2.426494</v>
+        <v>-2.426494</v>
       </c>
       <c r="O286" s="5" t="n">
-        <v>8.054671000000001</v>
+        <v>-8.054671000000001</v>
       </c>
       <c r="P286" t="inlineStr">
         <is>
@@ -37043,10 +37099,10 @@
         </is>
       </c>
       <c r="N287" s="5" t="n">
-        <v>2.225076</v>
+        <v>-2.225076</v>
       </c>
       <c r="O287" s="5" t="n">
-        <v>8.005869000000001</v>
+        <v>-8.005869000000001</v>
       </c>
       <c r="P287" t="inlineStr">
         <is>
@@ -37337,10 +37393,10 @@
         </is>
       </c>
       <c r="M290" s="5" t="n">
-        <v>2.006934</v>
+        <v>-2.006934</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>2.426494</v>
+        <v>-2.426494</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -37637,13 +37693,13 @@
         </is>
       </c>
       <c r="L293" s="5" t="n">
-        <v>0.844029</v>
+        <v>-0.844029</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>2.224292</v>
+        <v>-2.224292</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>2.225076</v>
+        <v>-2.225076</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -37932,10 +37988,10 @@
         </is>
       </c>
       <c r="L296" s="5" t="n">
-        <v>0.81027</v>
+        <v>-0.81027</v>
       </c>
       <c r="M296" s="5" t="n">
-        <v>2.006934</v>
+        <v>-2.006934</v>
       </c>
       <c r="N296" t="inlineStr">
         <is>
@@ -38823,19 +38879,19 @@
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>5.616703</v>
+        <v>-5.616703</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>2.879361</v>
+        <v>-2.879361</v>
       </c>
       <c r="J305" s="5" t="n">
-        <v>0.47328</v>
+        <v>-0.47328</v>
       </c>
       <c r="K305" s="5" t="n">
-        <v>6.118362</v>
+        <v>-6.118362</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>0.81027</v>
+        <v>-0.81027</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
@@ -39236,10 +39292,10 @@
         </is>
       </c>
       <c r="K309" s="5" t="n">
-        <v>4.324647</v>
+        <v>-4.324647</v>
       </c>
       <c r="L309" s="5" t="n">
-        <v>0.844029</v>
+        <v>-0.844029</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
@@ -40240,10 +40296,10 @@
         </is>
       </c>
       <c r="I319" s="5" t="n">
-        <v>2.879361</v>
+        <v>-2.879361</v>
       </c>
       <c r="J319" s="5" t="n">
-        <v>0.47328</v>
+        <v>-0.47328</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
@@ -41334,10 +41390,10 @@
         </is>
       </c>
       <c r="H330" s="5" t="n">
-        <v>5.355515</v>
+        <v>-5.355515</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>2.617846</v>
+        <v>-2.617846</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -42450,10 +42506,10 @@
         </is>
       </c>
       <c r="G341" s="5" t="n">
-        <v>2.600568</v>
+        <v>-2.600568</v>
       </c>
       <c r="H341" s="5" t="n">
-        <v>5.616703</v>
+        <v>-5.616703</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -42652,7 +42708,7 @@
         </is>
       </c>
       <c r="G343" s="5" t="n">
-        <v>0.424811</v>
+        <v>-0.424811</v>
       </c>
       <c r="H343" s="5" t="n">
         <v>-0.261188</v>
@@ -42755,10 +42811,10 @@
         </is>
       </c>
       <c r="G344" s="5" t="n">
-        <v>3.025379</v>
+        <v>-3.025379</v>
       </c>
       <c r="H344" s="5" t="n">
-        <v>5.355515</v>
+        <v>-5.355515</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AMY.xlsx
+++ b/output/pdf_financials_xlsx/AMY.xlsx
@@ -2499,10 +2499,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.306891</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.129004</v>
@@ -2535,16 +2533,16 @@
         <v>0.487132</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.256949</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.905644</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>21.294768</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.589483</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>17.124584</v>
@@ -2619,10 +2617,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.306891</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.129004</v>
@@ -2655,16 +2651,16 @@
         <v>0.487132</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.256949</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.905644</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>21.294768</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>19.589483</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>17.124584</v>
@@ -3371,16 +3367,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.329163</v>
+        <v>0.072214</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.721093</v>
+        <v>0.815449</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>21.415853</v>
+        <v>0.121085</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>19.663772</v>
+        <v>0.07428899999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.071213</v>
@@ -9469,7 +9465,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -12637,7 +12637,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -16939,7 +16943,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18644,7 +18652,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -22822,7 +22830,11 @@
           <t>Reclamation deposits, net</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
